--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.4865,0.2151,0.3212,0.0430</t>
-  </si>
-  <si>
-    <t>0.2914,0.0667,0.0712,0.6430</t>
-  </si>
-  <si>
-    <t>0.6370,0.2966,0.1194,0.0353</t>
-  </si>
-  <si>
-    <t>0.3111,0.1670,0.0550,0.6497</t>
-  </si>
-  <si>
-    <t>0.9864,0.0235,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9835,0.0271,0.0014,0.0011</t>
-  </si>
-  <si>
-    <t>0.9621,0.0554,0.0048,0.0017</t>
-  </si>
-  <si>
-    <t>0.9548,0.0562,0.0081,0.0037</t>
-  </si>
-  <si>
-    <t>0.9500,0.0863,0.0043,0.0015</t>
-  </si>
-  <si>
-    <t>0.9883,0.0174,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.9754,0.0347,0.0028,0.0017</t>
-  </si>
-  <si>
-    <t>0.9733,0.0396,0.0037,0.0021</t>
-  </si>
-  <si>
-    <t>0.4181,0.0646,0.6003,0.0349</t>
-  </si>
-  <si>
-    <t>0.3819,0.1185,0.5284,0.0172</t>
-  </si>
-  <si>
-    <t>0.2983,0.0847,0.7118,0.0054</t>
-  </si>
-  <si>
-    <t>0.1303,0.0155,0.9329,0.0071</t>
-  </si>
-  <si>
-    <t>0.4008,0.1159,0.5613,0.0197</t>
-  </si>
-  <si>
-    <t>0.0477,0.8967,0.1638,0.0029</t>
-  </si>
-  <si>
-    <t>0.0735,0.8843,0.0951,0.0018</t>
-  </si>
-  <si>
-    <t>0.5470,0.4937,0.0554,0.0077</t>
-  </si>
-  <si>
-    <t>0.0778,0.9023,0.0468,0.0012</t>
-  </si>
-  <si>
-    <t>0.0487,0.9257,0.0636,0.0009</t>
-  </si>
-  <si>
-    <t>0.3757,0.0322,0.7075,0.0283</t>
-  </si>
-  <si>
-    <t>0.3079,0.0865,0.6616,0.0953</t>
-  </si>
-  <si>
-    <t>0.0471,0.0247,0.9574,0.0102</t>
-  </si>
-  <si>
-    <t>0.1635,0.0153,0.9087,0.0160</t>
-  </si>
-  <si>
-    <t>0.0558,0.0610,0.9415,0.0036</t>
-  </si>
-  <si>
-    <t>0.1446,0.0733,0.8573,0.0121</t>
-  </si>
-  <si>
-    <t>0.0369,0.0156,0.9436,0.0375</t>
-  </si>
-  <si>
-    <t>0.1331,0.8425,0.0778,0.0054</t>
-  </si>
-  <si>
-    <t>0.3190,0.2408,0.4872,0.0126</t>
-  </si>
-  <si>
-    <t>0.0229,0.1414,0.9542,0.0086</t>
-  </si>
-  <si>
-    <t>0.0925,0.7794,0.2923,0.0121</t>
-  </si>
-  <si>
-    <t>0.5392,0.3084,0.2008,0.0253</t>
-  </si>
-  <si>
-    <t>0.5078,0.4750,0.0971,0.0262</t>
-  </si>
-  <si>
-    <t>0.4321,0.5154,0.0971,0.0050</t>
-  </si>
-  <si>
-    <t>0.0770,0.7029,0.4161,0.0031</t>
-  </si>
-  <si>
-    <t>0.0349,0.6854,0.7185,0.0198</t>
-  </si>
-  <si>
-    <t>0.0331,0.0423,0.9569,0.0145</t>
-  </si>
-  <si>
-    <t>0.0370,0.5374,0.7721,0.0165</t>
-  </si>
-  <si>
-    <t>0.2945,0.0940,0.6371,0.1013</t>
-  </si>
-  <si>
-    <t>0.0234,0.3570,0.8750,0.0053</t>
-  </si>
-  <si>
-    <t>0.0136,0.9196,0.3626,0.0043</t>
-  </si>
-  <si>
-    <t>0.0437,0.3135,0.8582,0.0057</t>
-  </si>
-  <si>
-    <t>0.3868,0.4007,0.2029,0.2130</t>
-  </si>
-  <si>
-    <t>0.0262,0.9339,0.1581,0.0072</t>
-  </si>
-  <si>
-    <t>0.0396,0.8639,0.4183,0.0106</t>
-  </si>
-  <si>
-    <t>0.0130,0.9542,0.2323,0.0018</t>
-  </si>
-  <si>
-    <t>0.0044,0.4520,0.9381,0.0025</t>
-  </si>
-  <si>
-    <t>0.0052,0.1148,0.9815,0.0017</t>
-  </si>
-  <si>
-    <t>0.1550,0.1914,0.7395,0.0122</t>
-  </si>
-  <si>
-    <t>0.0473,0.0557,0.9549,0.0042</t>
-  </si>
-  <si>
-    <t>0.0503,0.0632,0.9497,0.0033</t>
-  </si>
-  <si>
-    <t>0.0208,0.1418,0.9493,0.0031</t>
-  </si>
-  <si>
-    <t>0.9224,0.1264,0.0060,0.0020</t>
-  </si>
-  <si>
-    <t>0.8997,0.1104,0.0188,0.0072</t>
-  </si>
-  <si>
-    <t>0.9166,0.1050,0.0125,0.0025</t>
-  </si>
-  <si>
-    <t>0.0145,0.4893,0.8829,0.0033</t>
-  </si>
-  <si>
-    <t>0.9651,0.0387,0.0060,0.0035</t>
-  </si>
-  <si>
-    <t>0.9713,0.0351,0.0047,0.0022</t>
-  </si>
-  <si>
-    <t>0.9513,0.0828,0.0036,0.0011</t>
-  </si>
-  <si>
-    <t>0.0042,0.7741,0.8083,0.0017</t>
-  </si>
-  <si>
-    <t>0.0108,0.2635,0.9488,0.0056</t>
-  </si>
-  <si>
-    <t>0.0102,0.1456,0.9686,0.0028</t>
-  </si>
-  <si>
-    <t>0.0050,0.8460,0.7670,0.0026</t>
-  </si>
-  <si>
-    <t>0.0130,0.2327,0.9510,0.0023</t>
-  </si>
-  <si>
-    <t>0.0475,0.8184,0.2592,0.0042</t>
-  </si>
-  <si>
-    <t>0.0043,0.9854,0.0351,0.0010</t>
-  </si>
-  <si>
-    <t>0.3153,0.4375,0.3026,0.0073</t>
-  </si>
-  <si>
-    <t>0.3101,0.4944,0.2479,0.0090</t>
-  </si>
-  <si>
-    <t>0.0238,0.4345,0.8296,0.0034</t>
-  </si>
-  <si>
-    <t>0.0153,0.6590,0.8054,0.0052</t>
-  </si>
-  <si>
-    <t>0.0088,0.6151,0.8796,0.0032</t>
-  </si>
-  <si>
-    <t>0.0120,0.9393,0.2203,0.0056</t>
-  </si>
-  <si>
-    <t>0.0076,0.8394,0.6833,0.0040</t>
-  </si>
-  <si>
-    <t>0.0419,0.0080,0.0288,0.9504</t>
-  </si>
-  <si>
-    <t>0.0296,0.0273,0.0117,0.9732</t>
-  </si>
-  <si>
-    <t>0.0328,0.0698,0.0160,0.9680</t>
-  </si>
-  <si>
-    <t>0.0994,0.1345,0.0266,0.9029</t>
-  </si>
-  <si>
-    <t>0.0230,0.0775,0.0188,0.9701</t>
-  </si>
-  <si>
-    <t>0.0589,0.0510,0.0122,0.9495</t>
-  </si>
-  <si>
-    <t>0.0134,0.6391,0.8230,0.0079</t>
-  </si>
-  <si>
-    <t>0.0091,0.7924,0.7807,0.0038</t>
-  </si>
-  <si>
-    <t>0.0066,0.2858,0.9633,0.0015</t>
-  </si>
-  <si>
-    <t>0.0137,0.6178,0.8275,0.0061</t>
-  </si>
-  <si>
-    <t>0.0057,0.7625,0.8101,0.0013</t>
-  </si>
-  <si>
-    <t>0.0130,0.8573,0.5572,0.0041</t>
-  </si>
-  <si>
-    <t>0.9628,0.0470,0.0077,0.0026</t>
-  </si>
-  <si>
-    <t>0.9122,0.1265,0.0106,0.0023</t>
-  </si>
-  <si>
-    <t>0.9455,0.0907,0.0047,0.0011</t>
-  </si>
-  <si>
-    <t>0.9633,0.0470,0.0066,0.0026</t>
-  </si>
-  <si>
-    <t>0.9692,0.0465,0.0039,0.0016</t>
-  </si>
-  <si>
-    <t>0.9740,0.0543,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.9535,0.0656,0.0061,0.0018</t>
-  </si>
-  <si>
-    <t>0.9228,0.1373,0.0053,0.0021</t>
-  </si>
-  <si>
-    <t>0.9773,0.0340,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.9490,0.0816,0.0043,0.0017</t>
-  </si>
-  <si>
-    <t>0.9849,0.0145,0.0017,0.0033</t>
-  </si>
-  <si>
-    <t>0.9893,0.0148,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.9815,0.0310,0.0022,0.0009</t>
-  </si>
-  <si>
-    <t>0.9820,0.0271,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.9736,0.0378,0.0031,0.0020</t>
-  </si>
-  <si>
-    <t>0.9430,0.0951,0.0051,0.0019</t>
-  </si>
-  <si>
-    <t>0.0250,0.0755,0.9532,0.0111</t>
-  </si>
-  <si>
-    <t>0.0640,0.0478,0.9344,0.0056</t>
-  </si>
-  <si>
-    <t>0.2246,0.0419,0.8281,0.0267</t>
-  </si>
-  <si>
-    <t>0.2880,0.0302,0.7863,0.0118</t>
-  </si>
-  <si>
-    <t>0.1338,0.8773,0.0398,0.0022</t>
-  </si>
-  <si>
-    <t>0.0917,0.8832,0.0791,0.0021</t>
-  </si>
-  <si>
-    <t>0.0882,0.9109,0.0344,0.0021</t>
-  </si>
-  <si>
-    <t>0.2342,0.8297,0.0237,0.0029</t>
-  </si>
-  <si>
-    <t>0.1431,0.8351,0.0653,0.0021</t>
-  </si>
-  <si>
-    <t>0.1107,0.8978,0.0280,0.0019</t>
-  </si>
-  <si>
-    <t>0.2922,0.7582,0.0463,0.0032</t>
-  </si>
-  <si>
-    <t>0.4707,0.1015,0.4781,0.0124</t>
-  </si>
-  <si>
-    <t>0.3213,0.0396,0.7540,0.0114</t>
-  </si>
-  <si>
-    <t>0.2516,0.5375,0.3015,0.0301</t>
-  </si>
-  <si>
-    <t>0.4741,0.0644,0.5352,0.0276</t>
-  </si>
-  <si>
-    <t>0.3427,0.0940,0.1972,0.4901</t>
-  </si>
-  <si>
-    <t>0.0251,0.9302,0.2202,0.0032</t>
-  </si>
-  <si>
-    <t>0.0322,0.9044,0.2629,0.0054</t>
-  </si>
-  <si>
-    <t>0.2238,0.5736,0.2944,0.0146</t>
-  </si>
-  <si>
-    <t>0.0029,0.9739,0.3437,0.0008</t>
-  </si>
-  <si>
-    <t>0.0570,0.7819,0.3792,0.0021</t>
-  </si>
-  <si>
-    <t>0.2217,0.7692,0.0789,0.0067</t>
-  </si>
-  <si>
-    <t>0.2322,0.7783,0.0630,0.0026</t>
-  </si>
-  <si>
-    <t>0.7166,0.3352,0.0432,0.0059</t>
-  </si>
-  <si>
-    <t>0.9625,0.0506,0.0052,0.0054</t>
-  </si>
-  <si>
-    <t>0.9754,0.0295,0.0035,0.0028</t>
-  </si>
-  <si>
-    <t>0.9096,0.0785,0.0273,0.0101</t>
-  </si>
-  <si>
-    <t>0.9853,0.0199,0.0021,0.0017</t>
-  </si>
-  <si>
-    <t>0.6925,0.3247,0.0646,0.0041</t>
-  </si>
-  <si>
-    <t>0.8041,0.2612,0.0270,0.0053</t>
-  </si>
-  <si>
-    <t>0.9697,0.0357,0.0047,0.0029</t>
-  </si>
-  <si>
-    <t>0.0087,0.3776,0.9413,0.0031</t>
-  </si>
-  <si>
-    <t>0.0021,0.4980,0.9664,0.0008</t>
-  </si>
-  <si>
-    <t>0.0221,0.7603,0.6518,0.0087</t>
-  </si>
-  <si>
-    <t>0.0249,0.2874,0.9032,0.0039</t>
-  </si>
-  <si>
-    <t>0.3993,0.1394,0.4966,0.0317</t>
-  </si>
-  <si>
-    <t>0.3816,0.1699,0.5416,0.0341</t>
-  </si>
-  <si>
-    <t>0.4085,0.1248,0.5246,0.0298</t>
-  </si>
-  <si>
-    <t>0.3829,0.4215,0.2383,0.0248</t>
-  </si>
-  <si>
-    <t>0.1560,0.0835,0.0510,0.8314</t>
-  </si>
-  <si>
-    <t>0.0019,0.0051,0.0006,0.9985</t>
-  </si>
-  <si>
-    <t>0.0386,0.0650,0.0183,0.9626</t>
-  </si>
-  <si>
-    <t>0.0985,0.0621,0.0243,0.9105</t>
-  </si>
-  <si>
-    <t>0.0117,0.8882,0.5143,0.0056</t>
-  </si>
-  <si>
-    <t>0.9480,0.0576,0.0119,0.0033</t>
-  </si>
-  <si>
-    <t>0.7464,0.2242,0.0724,0.0090</t>
-  </si>
-  <si>
-    <t>0.6936,0.4009,0.0261,0.0063</t>
-  </si>
-  <si>
-    <t>0.7573,0.3591,0.0143,0.0023</t>
-  </si>
-  <si>
-    <t>0.8943,0.1206,0.0176,0.0101</t>
-  </si>
-  <si>
-    <t>0.6000,0.1599,0.2354,0.0578</t>
-  </si>
-  <si>
-    <t>0.7020,0.3837,0.0363,0.0031</t>
-  </si>
-  <si>
-    <t>0.0102,0.1352,0.9666,0.0075</t>
-  </si>
-  <si>
-    <t>0.8470,0.1039,0.0576,0.0414</t>
-  </si>
-  <si>
-    <t>0.4663,0.4099,0.1826,0.0063</t>
-  </si>
-  <si>
-    <t>0.0999,0.7929,0.2094,0.0085</t>
-  </si>
-  <si>
-    <t>0.4256,0.4134,0.2158,0.0166</t>
-  </si>
-  <si>
-    <t>0.4736,0.4166,0.1559,0.0154</t>
-  </si>
-  <si>
-    <t>0.3490,0.5117,0.1851,0.0278</t>
-  </si>
-  <si>
-    <t>0.2417,0.5730,0.2319,0.0060</t>
-  </si>
-  <si>
-    <t>0.3145,0.6027,0.1254,0.0155</t>
-  </si>
-  <si>
-    <t>0.9697,0.0409,0.0042,0.0028</t>
-  </si>
-  <si>
-    <t>0.9810,0.0251,0.0021,0.0022</t>
-  </si>
-  <si>
-    <t>0.9828,0.0255,0.0018,0.0015</t>
-  </si>
-  <si>
-    <t>0.9038,0.1483,0.0082,0.0027</t>
-  </si>
-  <si>
-    <t>0.6336,0.4009,0.0487,0.0034</t>
-  </si>
-  <si>
-    <t>0.9746,0.0290,0.0043,0.0033</t>
-  </si>
-  <si>
-    <t>0.9865,0.0144,0.0018,0.0022</t>
-  </si>
-  <si>
-    <t>0.9568,0.0632,0.0057,0.0029</t>
-  </si>
-  <si>
-    <t>0.1343,0.8595,0.0553,0.0035</t>
-  </si>
-  <si>
-    <t>0.6034,0.4913,0.0263,0.0019</t>
-  </si>
-  <si>
-    <t>0.2323,0.8094,0.0329,0.0023</t>
-  </si>
-  <si>
-    <t>0.3706,0.2724,0.3701,0.0061</t>
-  </si>
-  <si>
-    <t>0.7817,0.2626,0.0327,0.0057</t>
-  </si>
-  <si>
-    <t>0.7014,0.4482,0.0176,0.0027</t>
-  </si>
-  <si>
-    <t>0.8118,0.2576,0.0188,0.0023</t>
-  </si>
-  <si>
-    <t>0.9143,0.1174,0.0091,0.0031</t>
-  </si>
-  <si>
-    <t>0.0369,0.0994,0.9573,0.0056</t>
-  </si>
-  <si>
-    <t>0.8024,0.2426,0.0271,0.0026</t>
-  </si>
-  <si>
-    <t>0.0189,0.0213,0.9847,0.0030</t>
-  </si>
-  <si>
-    <t>0.0183,0.0691,0.9714,0.0054</t>
-  </si>
-  <si>
-    <t>0.1922,0.1244,0.7561,0.0126</t>
-  </si>
-  <si>
-    <t>0.0148,0.2899,0.9447,0.0034</t>
-  </si>
-  <si>
-    <t>0.0282,0.0187,0.9816,0.0017</t>
-  </si>
-  <si>
-    <t>0.1585,0.0272,0.8918,0.0064</t>
-  </si>
-  <si>
-    <t>0.0190,0.0300,0.9795,0.0035</t>
-  </si>
-  <si>
-    <t>0.3592,0.2531,0.4385,0.0155</t>
-  </si>
-  <si>
-    <t>0.1461,0.0688,0.8633,0.0090</t>
-  </si>
-  <si>
-    <t>0.4520,0.2045,0.3745,0.0275</t>
-  </si>
-  <si>
-    <t>0.1444,0.5257,0.4337,0.0053</t>
-  </si>
-  <si>
-    <t>0.1813,0.4684,0.3951,0.0072</t>
-  </si>
-  <si>
-    <t>0.1595,0.4419,0.5402,0.0095</t>
-  </si>
-  <si>
-    <t>0.3493,0.1087,0.5919,0.0175</t>
-  </si>
-  <si>
-    <t>0.4570,0.0760,0.5406,0.0148</t>
-  </si>
-  <si>
-    <t>0.3928,0.6612,0.0579,0.0040</t>
-  </si>
-  <si>
-    <t>0.4554,0.5614,0.0690,0.0048</t>
-  </si>
-  <si>
-    <t>0.5103,0.5717,0.0443,0.0042</t>
-  </si>
-  <si>
-    <t>0.9421,0.0885,0.0073,0.0016</t>
-  </si>
-  <si>
-    <t>0.9208,0.0968,0.0125,0.0042</t>
-  </si>
-  <si>
-    <t>0.3395,0.1980,0.5585,0.0319</t>
-  </si>
-  <si>
-    <t>0.5029,0.1279,0.4031,0.0137</t>
-  </si>
-  <si>
-    <t>0.3602,0.0913,0.1962,0.4123</t>
-  </si>
-  <si>
-    <t>0.2505,0.1826,0.6845,0.0143</t>
-  </si>
-  <si>
-    <t>0.4391,0.0997,0.5159,0.0199</t>
-  </si>
-  <si>
-    <t>0.1761,0.2147,0.7001,0.0247</t>
-  </si>
-  <si>
-    <t>0.0537,0.3086,0.8645,0.0159</t>
-  </si>
-  <si>
-    <t>0.0524,0.2663,0.8824,0.0136</t>
-  </si>
-  <si>
-    <t>0.0382,0.2491,0.8963,0.0083</t>
-  </si>
-  <si>
-    <t>0.0098,0.1954,0.9567,0.0051</t>
-  </si>
-  <si>
-    <t>0.9729,0.0368,0.0034,0.0024</t>
-  </si>
-  <si>
-    <t>0.9627,0.0481,0.0063,0.0023</t>
-  </si>
-  <si>
-    <t>0.9810,0.0269,0.0021,0.0016</t>
-  </si>
-  <si>
-    <t>0.9793,0.0234,0.0038,0.0021</t>
-  </si>
-  <si>
-    <t>0.9654,0.0552,0.0039,0.0011</t>
-  </si>
-  <si>
-    <t>0.9622,0.0658,0.0034,0.0008</t>
-  </si>
-  <si>
-    <t>0.9807,0.0239,0.0023,0.0024</t>
-  </si>
-  <si>
-    <t>0.9462,0.0646,0.0063,0.0045</t>
-  </si>
-  <si>
-    <t>0.3162,0.0724,0.7205,0.0092</t>
-  </si>
-  <si>
-    <t>0.5096,0.2127,0.2979,0.0090</t>
-  </si>
-  <si>
-    <t>0.6875,0.3283,0.0620,0.0209</t>
-  </si>
-  <si>
-    <t>0.0238,0.0608,0.9662,0.0038</t>
-  </si>
-  <si>
-    <t>0.0280,0.0584,0.9631,0.0042</t>
-  </si>
-  <si>
-    <t>0.0638,0.1749,0.8695,0.0080</t>
-  </si>
-  <si>
-    <t>0.0027,0.0615,0.9910,0.0015</t>
-  </si>
-  <si>
-    <t>0.1093,0.0684,0.8850,0.0109</t>
-  </si>
-  <si>
-    <t>0.0049,0.3450,0.9564,0.0034</t>
-  </si>
-  <si>
-    <t>0.0325,0.0199,0.9776,0.0030</t>
-  </si>
-  <si>
-    <t>0.4040,0.1758,0.4481,0.0193</t>
-  </si>
-  <si>
-    <t>0.4568,0.1098,0.4280,0.1158</t>
-  </si>
-  <si>
-    <t>0.3385,0.0322,0.7193,0.0360</t>
-  </si>
-  <si>
-    <t>0.3648,0.0455,0.5952,0.1192</t>
-  </si>
-  <si>
-    <t>0.4605,0.6555,0.0270,0.0031</t>
-  </si>
-  <si>
-    <t>0.9847,0.0270,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9570,0.0544,0.0069,0.0018</t>
-  </si>
-  <si>
-    <t>0.9457,0.0962,0.0038,0.0009</t>
-  </si>
-  <si>
-    <t>0.9515,0.0748,0.0045,0.0016</t>
-  </si>
-  <si>
-    <t>0.9597,0.0612,0.0047,0.0017</t>
-  </si>
-  <si>
-    <t>0.9772,0.0356,0.0022,0.0014</t>
-  </si>
-  <si>
-    <t>0.9225,0.1295,0.0075,0.0011</t>
-  </si>
-  <si>
-    <t>0.0404,0.0514,0.9519,0.0061</t>
-  </si>
-  <si>
-    <t>0.0140,0.1663,0.9531,0.0048</t>
-  </si>
-  <si>
-    <t>0.0212,0.2587,0.9212,0.0043</t>
-  </si>
-  <si>
-    <t>0.3140,0.0855,0.6747,0.0365</t>
-  </si>
-  <si>
-    <t>0.0291,0.0526,0.9631,0.0071</t>
-  </si>
-  <si>
-    <t>0.2402,0.0262,0.8290,0.0225</t>
-  </si>
-  <si>
-    <t>0.3799,0.0746,0.4437,0.2097</t>
-  </si>
-  <si>
-    <t>0.0936,0.1829,0.8275,0.0316</t>
-  </si>
-  <si>
-    <t>0.6729,0.1140,0.2067,0.0534</t>
-  </si>
-  <si>
-    <t>0.3354,0.1091,0.3575,0.3646</t>
-  </si>
-  <si>
-    <t>0.1378,0.0390,0.0032,0.9005</t>
-  </si>
-  <si>
-    <t>0.0186,0.0170,0.0028,0.9858</t>
-  </si>
-  <si>
-    <t>0.0933,0.0150,0.0052,0.9350</t>
-  </si>
-  <si>
-    <t>0.3969,0.0460,0.6455,0.0512</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.3843,0.5590,0.0922,0.0677</t>
+  </si>
+  <si>
+    <t>0.0978,0.0309,0.0265,0.9171</t>
+  </si>
+  <si>
+    <t>0.5997,0.1322,0.2718,0.0720</t>
+  </si>
+  <si>
+    <t>0.1356,0.0741,0.0417,0.8617</t>
+  </si>
+  <si>
+    <t>0.9821,0.0301,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9867,0.0190,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9554,0.0693,0.0044,0.0017</t>
+  </si>
+  <si>
+    <t>0.9765,0.0296,0.0038,0.0019</t>
+  </si>
+  <si>
+    <t>0.9810,0.0277,0.0024,0.0014</t>
+  </si>
+  <si>
+    <t>0.9752,0.0362,0.0029,0.0011</t>
+  </si>
+  <si>
+    <t>0.9803,0.0202,0.0039,0.0028</t>
+  </si>
+  <si>
+    <t>0.9617,0.0553,0.0065,0.0017</t>
+  </si>
+  <si>
+    <t>0.4472,0.2077,0.3985,0.0824</t>
+  </si>
+  <si>
+    <t>0.2535,0.0606,0.7649,0.0067</t>
+  </si>
+  <si>
+    <t>0.2781,0.0439,0.7895,0.0083</t>
+  </si>
+  <si>
+    <t>0.3412,0.0616,0.6610,0.0538</t>
+  </si>
+  <si>
+    <t>0.4428,0.1106,0.4889,0.0740</t>
+  </si>
+  <si>
+    <t>0.0947,0.8305,0.1762,0.0040</t>
+  </si>
+  <si>
+    <t>0.0407,0.9379,0.0665,0.0010</t>
+  </si>
+  <si>
+    <t>0.5733,0.3337,0.1147,0.0038</t>
+  </si>
+  <si>
+    <t>0.0929,0.9040,0.0419,0.0023</t>
+  </si>
+  <si>
+    <t>0.1487,0.8537,0.0434,0.0023</t>
+  </si>
+  <si>
+    <t>0.3132,0.0548,0.7105,0.0305</t>
+  </si>
+  <si>
+    <t>0.4201,0.1360,0.4734,0.0580</t>
+  </si>
+  <si>
+    <t>0.0535,0.0264,0.9551,0.0098</t>
+  </si>
+  <si>
+    <t>0.2203,0.0555,0.7885,0.0252</t>
+  </si>
+  <si>
+    <t>0.1786,0.0324,0.8483,0.0394</t>
+  </si>
+  <si>
+    <t>0.1800,0.0166,0.8922,0.0133</t>
+  </si>
+  <si>
+    <t>0.0070,0.0063,0.9921,0.0024</t>
+  </si>
+  <si>
+    <t>0.1708,0.7303,0.1425,0.0072</t>
+  </si>
+  <si>
+    <t>0.5675,0.2174,0.2532,0.0224</t>
+  </si>
+  <si>
+    <t>0.0144,0.1081,0.9685,0.0041</t>
+  </si>
+  <si>
+    <t>0.0890,0.6710,0.3931,0.0052</t>
+  </si>
+  <si>
+    <t>0.4945,0.3670,0.1824,0.0177</t>
+  </si>
+  <si>
+    <t>0.4281,0.4404,0.1518,0.0076</t>
+  </si>
+  <si>
+    <t>0.1942,0.8315,0.0468,0.0023</t>
+  </si>
+  <si>
+    <t>0.1755,0.3894,0.5445,0.0056</t>
+  </si>
+  <si>
+    <t>0.0198,0.8427,0.5775,0.0090</t>
+  </si>
+  <si>
+    <t>0.0412,0.2648,0.8929,0.0145</t>
+  </si>
+  <si>
+    <t>0.0501,0.1381,0.8998,0.0120</t>
+  </si>
+  <si>
+    <t>0.0682,0.0607,0.9325,0.0130</t>
+  </si>
+  <si>
+    <t>0.0533,0.2529,0.8675,0.0062</t>
+  </si>
+  <si>
+    <t>0.0186,0.8513,0.4715,0.0079</t>
+  </si>
+  <si>
+    <t>0.0461,0.2355,0.8740,0.0167</t>
+  </si>
+  <si>
+    <t>0.2911,0.3156,0.1416,0.4491</t>
+  </si>
+  <si>
+    <t>0.0542,0.8606,0.2928,0.0087</t>
+  </si>
+  <si>
+    <t>0.0165,0.9087,0.4199,0.0033</t>
+  </si>
+  <si>
+    <t>0.0153,0.9566,0.1543,0.0021</t>
+  </si>
+  <si>
+    <t>0.0077,0.6625,0.8670,0.0040</t>
+  </si>
+  <si>
+    <t>0.0044,0.2072,0.9764,0.0016</t>
+  </si>
+  <si>
+    <t>0.0494,0.0535,0.9497,0.0047</t>
+  </si>
+  <si>
+    <t>0.0265,0.0185,0.9802,0.0022</t>
+  </si>
+  <si>
+    <t>0.0383,0.0829,0.9480,0.0034</t>
+  </si>
+  <si>
+    <t>0.0185,0.2085,0.9382,0.0015</t>
+  </si>
+  <si>
+    <t>0.8808,0.1620,0.0112,0.0054</t>
+  </si>
+  <si>
+    <t>0.9255,0.0691,0.0225,0.0051</t>
+  </si>
+  <si>
+    <t>0.9635,0.0514,0.0043,0.0017</t>
+  </si>
+  <si>
+    <t>0.0358,0.3943,0.8457,0.0062</t>
+  </si>
+  <si>
+    <t>0.9247,0.1162,0.0079,0.0020</t>
+  </si>
+  <si>
+    <t>0.9712,0.0517,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.6686,0.4309,0.0304,0.0021</t>
+  </si>
+  <si>
+    <t>0.0036,0.5517,0.9278,0.0017</t>
+  </si>
+  <si>
+    <t>0.0058,0.1453,0.9737,0.0046</t>
+  </si>
+  <si>
+    <t>0.0262,0.1969,0.9198,0.0076</t>
+  </si>
+  <si>
+    <t>0.0049,0.9045,0.6281,0.0016</t>
+  </si>
+  <si>
+    <t>0.0074,0.0365,0.9892,0.0008</t>
+  </si>
+  <si>
+    <t>0.0825,0.8222,0.1569,0.0050</t>
+  </si>
+  <si>
+    <t>0.0053,0.9826,0.0535,0.0008</t>
+  </si>
+  <si>
+    <t>0.4888,0.2522,0.2949,0.0187</t>
+  </si>
+  <si>
+    <t>0.2003,0.6197,0.1974,0.0063</t>
+  </si>
+  <si>
+    <t>0.0421,0.1302,0.9354,0.0047</t>
+  </si>
+  <si>
+    <t>0.0057,0.5483,0.9058,0.0020</t>
+  </si>
+  <si>
+    <t>0.0072,0.6764,0.8497,0.0024</t>
+  </si>
+  <si>
+    <t>0.0029,0.8134,0.7843,0.0016</t>
+  </si>
+  <si>
+    <t>0.0079,0.9083,0.5206,0.0031</t>
+  </si>
+  <si>
+    <t>0.1737,0.0122,0.0655,0.7818</t>
+  </si>
+  <si>
+    <t>0.0494,0.0282,0.0236,0.9518</t>
+  </si>
+  <si>
+    <t>0.0038,0.0133,0.0009,0.9968</t>
+  </si>
+  <si>
+    <t>0.0087,0.0159,0.0020,0.9933</t>
+  </si>
+  <si>
+    <t>0.0138,0.0533,0.0103,0.9848</t>
+  </si>
+  <si>
+    <t>0.0266,0.0542,0.0083,0.9759</t>
+  </si>
+  <si>
+    <t>0.0065,0.8950,0.6022,0.0028</t>
+  </si>
+  <si>
+    <t>0.0059,0.3901,0.9443,0.0046</t>
+  </si>
+  <si>
+    <t>0.0238,0.2634,0.9210,0.0109</t>
+  </si>
+  <si>
+    <t>0.0054,0.5194,0.9250,0.0019</t>
+  </si>
+  <si>
+    <t>0.0022,0.8262,0.8051,0.0005</t>
+  </si>
+  <si>
+    <t>0.0093,0.7717,0.7529,0.0030</t>
+  </si>
+  <si>
+    <t>0.9398,0.0945,0.0054,0.0016</t>
+  </si>
+  <si>
+    <t>0.9303,0.1269,0.0049,0.0017</t>
+  </si>
+  <si>
+    <t>0.9851,0.0201,0.0022,0.0016</t>
+  </si>
+  <si>
+    <t>0.9826,0.0212,0.0028,0.0021</t>
+  </si>
+  <si>
+    <t>0.9599,0.0784,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.9110,0.1316,0.0119,0.0016</t>
+  </si>
+  <si>
+    <t>0.9245,0.1351,0.0043,0.0012</t>
+  </si>
+  <si>
+    <t>0.9489,0.0972,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.9809,0.0253,0.0023,0.0015</t>
+  </si>
+  <si>
+    <t>0.9732,0.0419,0.0036,0.0008</t>
+  </si>
+  <si>
+    <t>0.9739,0.0415,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.9756,0.0405,0.0026,0.0013</t>
+  </si>
+  <si>
+    <t>0.9819,0.0229,0.0029,0.0018</t>
+  </si>
+  <si>
+    <t>0.9850,0.0229,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.9836,0.0202,0.0019,0.0025</t>
+  </si>
+  <si>
+    <t>0.9727,0.0342,0.0038,0.0029</t>
+  </si>
+  <si>
+    <t>0.0232,0.0178,0.9704,0.0123</t>
+  </si>
+  <si>
+    <t>0.1397,0.0808,0.8655,0.0083</t>
+  </si>
+  <si>
+    <t>0.3239,0.0390,0.6874,0.0845</t>
+  </si>
+  <si>
+    <t>0.1290,0.0375,0.8883,0.0277</t>
+  </si>
+  <si>
+    <t>0.2479,0.7580,0.0573,0.0046</t>
+  </si>
+  <si>
+    <t>0.0845,0.8976,0.0591,0.0013</t>
+  </si>
+  <si>
+    <t>0.1323,0.8760,0.0357,0.0021</t>
+  </si>
+  <si>
+    <t>0.1571,0.8407,0.0619,0.0047</t>
+  </si>
+  <si>
+    <t>0.0813,0.8966,0.0755,0.0023</t>
+  </si>
+  <si>
+    <t>0.0904,0.8889,0.0601,0.0031</t>
+  </si>
+  <si>
+    <t>0.3927,0.6134,0.0746,0.0033</t>
+  </si>
+  <si>
+    <t>0.4096,0.3276,0.3305,0.0302</t>
+  </si>
+  <si>
+    <t>0.4166,0.0455,0.5994,0.0406</t>
+  </si>
+  <si>
+    <t>0.3137,0.4673,0.3090,0.0579</t>
+  </si>
+  <si>
+    <t>0.2866,0.0337,0.7925,0.0106</t>
+  </si>
+  <si>
+    <t>0.4885,0.0993,0.4548,0.1316</t>
+  </si>
+  <si>
+    <t>0.0227,0.9368,0.1915,0.0026</t>
+  </si>
+  <si>
+    <t>0.0179,0.9456,0.1869,0.0026</t>
+  </si>
+  <si>
+    <t>0.1791,0.6580,0.2568,0.0135</t>
+  </si>
+  <si>
+    <t>0.0025,0.9816,0.2308,0.0006</t>
+  </si>
+  <si>
+    <t>0.0913,0.7529,0.3256,0.0029</t>
+  </si>
+  <si>
+    <t>0.4069,0.5154,0.1153,0.0051</t>
+  </si>
+  <si>
+    <t>0.2629,0.7878,0.0396,0.0039</t>
+  </si>
+  <si>
+    <t>0.7752,0.2406,0.0415,0.0065</t>
+  </si>
+  <si>
+    <t>0.9690,0.0314,0.0053,0.0052</t>
+  </si>
+  <si>
+    <t>0.9609,0.0453,0.0051,0.0070</t>
+  </si>
+  <si>
+    <t>0.8891,0.1399,0.0139,0.0098</t>
+  </si>
+  <si>
+    <t>0.9782,0.0200,0.0032,0.0064</t>
+  </si>
+  <si>
+    <t>0.5325,0.5387,0.0441,0.0051</t>
+  </si>
+  <si>
+    <t>0.9729,0.0330,0.0040,0.0022</t>
+  </si>
+  <si>
+    <t>0.9605,0.0578,0.0063,0.0022</t>
+  </si>
+  <si>
+    <t>0.0079,0.5974,0.8944,0.0037</t>
+  </si>
+  <si>
+    <t>0.0090,0.5473,0.8984,0.0028</t>
+  </si>
+  <si>
+    <t>0.0104,0.5418,0.8914,0.0036</t>
+  </si>
+  <si>
+    <t>0.0235,0.3637,0.8834,0.0058</t>
+  </si>
+  <si>
+    <t>0.5131,0.1939,0.3439,0.0514</t>
+  </si>
+  <si>
+    <t>0.4838,0.1765,0.3939,0.0415</t>
+  </si>
+  <si>
+    <t>0.2853,0.0698,0.7550,0.0102</t>
+  </si>
+  <si>
+    <t>0.4244,0.1278,0.4902,0.0430</t>
+  </si>
+  <si>
+    <t>0.1036,0.1002,0.0545,0.8794</t>
+  </si>
+  <si>
+    <t>0.0075,0.0141,0.0024,0.9935</t>
+  </si>
+  <si>
+    <t>0.0488,0.1048,0.0270,0.9441</t>
+  </si>
+  <si>
+    <t>0.1955,0.1034,0.0512,0.8035</t>
+  </si>
+  <si>
+    <t>0.0084,0.8585,0.6499,0.0042</t>
+  </si>
+  <si>
+    <t>0.9016,0.1451,0.0111,0.0031</t>
+  </si>
+  <si>
+    <t>0.5855,0.4726,0.0529,0.0091</t>
+  </si>
+  <si>
+    <t>0.9712,0.0274,0.0041,0.0056</t>
+  </si>
+  <si>
+    <t>0.5139,0.6256,0.0160,0.0028</t>
+  </si>
+  <si>
+    <t>0.8099,0.2411,0.0213,0.0060</t>
+  </si>
+  <si>
+    <t>0.5413,0.3308,0.1771,0.0603</t>
+  </si>
+  <si>
+    <t>0.7854,0.3249,0.0202,0.0025</t>
+  </si>
+  <si>
+    <t>0.0094,0.1199,0.9691,0.0073</t>
+  </si>
+  <si>
+    <t>0.6304,0.2136,0.1809,0.0129</t>
+  </si>
+  <si>
+    <t>0.8259,0.1654,0.0547,0.0154</t>
+  </si>
+  <si>
+    <t>0.2123,0.7402,0.0982,0.0124</t>
+  </si>
+  <si>
+    <t>0.5403,0.3092,0.1867,0.0132</t>
+  </si>
+  <si>
+    <t>0.3349,0.3134,0.3753,0.0081</t>
+  </si>
+  <si>
+    <t>0.3790,0.4144,0.2771,0.0219</t>
+  </si>
+  <si>
+    <t>0.2888,0.4168,0.3103,0.0061</t>
+  </si>
+  <si>
+    <t>0.3434,0.5310,0.2069,0.0169</t>
+  </si>
+  <si>
+    <t>0.9597,0.0571,0.0055,0.0026</t>
+  </si>
+  <si>
+    <t>0.9060,0.1362,0.0100,0.0031</t>
+  </si>
+  <si>
+    <t>0.9673,0.0417,0.0058,0.0020</t>
+  </si>
+  <si>
+    <t>0.9592,0.0697,0.0030,0.0014</t>
+  </si>
+  <si>
+    <t>0.9498,0.0527,0.0138,0.0046</t>
+  </si>
+  <si>
+    <t>0.9227,0.0922,0.0146,0.0027</t>
+  </si>
+  <si>
+    <t>0.9532,0.0611,0.0052,0.0051</t>
+  </si>
+  <si>
+    <t>0.9518,0.0693,0.0052,0.0019</t>
+  </si>
+  <si>
+    <t>0.0867,0.8606,0.1295,0.0048</t>
+  </si>
+  <si>
+    <t>0.4741,0.6170,0.0278,0.0025</t>
+  </si>
+  <si>
+    <t>0.2087,0.8230,0.0398,0.0027</t>
+  </si>
+  <si>
+    <t>0.2260,0.1707,0.6836,0.0053</t>
+  </si>
+  <si>
+    <t>0.9582,0.0596,0.0043,0.0025</t>
+  </si>
+  <si>
+    <t>0.3992,0.6800,0.0390,0.0039</t>
+  </si>
+  <si>
+    <t>0.7454,0.2677,0.0581,0.0034</t>
+  </si>
+  <si>
+    <t>0.8012,0.2883,0.0178,0.0030</t>
+  </si>
+  <si>
+    <t>0.0292,0.1209,0.9531,0.0025</t>
+  </si>
+  <si>
+    <t>0.8844,0.1630,0.0127,0.0029</t>
+  </si>
+  <si>
+    <t>0.0208,0.0273,0.9811,0.0022</t>
+  </si>
+  <si>
+    <t>0.0183,0.1160,0.9657,0.0041</t>
+  </si>
+  <si>
+    <t>0.2008,0.1506,0.7143,0.0074</t>
+  </si>
+  <si>
+    <t>0.0070,0.4128,0.9297,0.0019</t>
+  </si>
+  <si>
+    <t>0.1409,0.0264,0.9102,0.0176</t>
+  </si>
+  <si>
+    <t>0.0597,0.0114,0.9646,0.0075</t>
+  </si>
+  <si>
+    <t>0.0508,0.0806,0.9404,0.0038</t>
+  </si>
+  <si>
+    <t>0.4625,0.0685,0.4946,0.0284</t>
+  </si>
+  <si>
+    <t>0.2759,0.1158,0.6853,0.0113</t>
+  </si>
+  <si>
+    <t>0.4397,0.1515,0.4650,0.0204</t>
+  </si>
+  <si>
+    <t>0.2653,0.1805,0.5770,0.0116</t>
+  </si>
+  <si>
+    <t>0.2111,0.1873,0.6902,0.0069</t>
+  </si>
+  <si>
+    <t>0.2616,0.0454,0.7887,0.0141</t>
+  </si>
+  <si>
+    <t>0.5087,0.1516,0.3594,0.0489</t>
+  </si>
+  <si>
+    <t>0.4597,0.0845,0.4956,0.0360</t>
+  </si>
+  <si>
+    <t>0.7113,0.3180,0.0445,0.0067</t>
+  </si>
+  <si>
+    <t>0.6739,0.4325,0.0266,0.0036</t>
+  </si>
+  <si>
+    <t>0.5008,0.6173,0.0280,0.0026</t>
+  </si>
+  <si>
+    <t>0.9144,0.1273,0.0081,0.0017</t>
+  </si>
+  <si>
+    <t>0.7550,0.3737,0.0123,0.0023</t>
+  </si>
+  <si>
+    <t>0.4023,0.1902,0.4675,0.0166</t>
+  </si>
+  <si>
+    <t>0.3718,0.1053,0.5807,0.0187</t>
+  </si>
+  <si>
+    <t>0.4385,0.1425,0.4538,0.1008</t>
+  </si>
+  <si>
+    <t>0.4293,0.1258,0.4975,0.0688</t>
+  </si>
+  <si>
+    <t>0.2995,0.3209,0.4367,0.0101</t>
+  </si>
+  <si>
+    <t>0.3485,0.1006,0.5892,0.0628</t>
+  </si>
+  <si>
+    <t>0.0735,0.2003,0.8540,0.0161</t>
+  </si>
+  <si>
+    <t>0.0187,0.3205,0.9222,0.0049</t>
+  </si>
+  <si>
+    <t>0.0310,0.1307,0.9451,0.0069</t>
+  </si>
+  <si>
+    <t>0.0159,0.4909,0.8750,0.0046</t>
+  </si>
+  <si>
+    <t>0.9828,0.0231,0.0023,0.0017</t>
+  </si>
+  <si>
+    <t>0.9645,0.0567,0.0040,0.0011</t>
+  </si>
+  <si>
+    <t>0.9628,0.0542,0.0056,0.0021</t>
+  </si>
+  <si>
+    <t>0.9108,0.1384,0.0082,0.0019</t>
+  </si>
+  <si>
+    <t>0.9496,0.0716,0.0056,0.0017</t>
+  </si>
+  <si>
+    <t>0.9334,0.1026,0.0059,0.0020</t>
+  </si>
+  <si>
+    <t>0.9702,0.0520,0.0023,0.0013</t>
+  </si>
+  <si>
+    <t>0.9728,0.0365,0.0039,0.0024</t>
+  </si>
+  <si>
+    <t>0.0458,0.0554,0.9568,0.0031</t>
+  </si>
+  <si>
+    <t>0.4535,0.1887,0.3979,0.0096</t>
+  </si>
+  <si>
+    <t>0.4687,0.1424,0.4639,0.0302</t>
+  </si>
+  <si>
+    <t>0.0101,0.1125,0.9756,0.0019</t>
+  </si>
+  <si>
+    <t>0.0095,0.1440,0.9697,0.0017</t>
+  </si>
+  <si>
+    <t>0.0335,0.2844,0.8819,0.0038</t>
+  </si>
+  <si>
+    <t>0.0087,0.1497,0.9734,0.0020</t>
+  </si>
+  <si>
+    <t>0.1990,0.0806,0.7901,0.0138</t>
+  </si>
+  <si>
+    <t>0.0038,0.0377,0.9900,0.0025</t>
+  </si>
+  <si>
+    <t>0.0703,0.0409,0.9341,0.0071</t>
+  </si>
+  <si>
+    <t>0.2331,0.1001,0.7402,0.0128</t>
+  </si>
+  <si>
+    <t>0.4447,0.0954,0.5384,0.0242</t>
+  </si>
+  <si>
+    <t>0.3279,0.0602,0.6869,0.0162</t>
+  </si>
+  <si>
+    <t>0.4549,0.0652,0.5585,0.0196</t>
+  </si>
+  <si>
+    <t>0.9472,0.0937,0.0041,0.0010</t>
+  </si>
+  <si>
+    <t>0.9698,0.0484,0.0036,0.0015</t>
+  </si>
+  <si>
+    <t>0.9752,0.0355,0.0024,0.0016</t>
+  </si>
+  <si>
+    <t>0.9076,0.1400,0.0106,0.0019</t>
+  </si>
+  <si>
+    <t>0.9744,0.0352,0.0041,0.0016</t>
+  </si>
+  <si>
+    <t>0.8100,0.2939,0.0113,0.0019</t>
+  </si>
+  <si>
+    <t>0.9687,0.0463,0.0031,0.0016</t>
+  </si>
+  <si>
+    <t>0.9058,0.1556,0.0072,0.0014</t>
+  </si>
+  <si>
+    <t>0.0541,0.0678,0.9337,0.0065</t>
+  </si>
+  <si>
+    <t>0.0335,0.2246,0.9065,0.0052</t>
+  </si>
+  <si>
+    <t>0.0190,0.1155,0.9594,0.0029</t>
+  </si>
+  <si>
+    <t>0.1184,0.0741,0.8790,0.0104</t>
+  </si>
+  <si>
+    <t>0.0177,0.0243,0.9801,0.0047</t>
+  </si>
+  <si>
+    <t>0.3652,0.0387,0.6597,0.0644</t>
+  </si>
+  <si>
+    <t>0.2655,0.0356,0.7505,0.0654</t>
+  </si>
+  <si>
+    <t>0.0322,0.2601,0.9088,0.0110</t>
+  </si>
+  <si>
+    <t>0.7587,0.1541,0.0939,0.0452</t>
+  </si>
+  <si>
+    <t>0.1790,0.0723,0.2004,0.7067</t>
+  </si>
+  <si>
+    <t>0.1276,0.0644,0.0420,0.8842</t>
+  </si>
+  <si>
+    <t>0.0632,0.0111,0.0072,0.9538</t>
+  </si>
+  <si>
+    <t>0.0303,0.0131,0.0022,0.9794</t>
+  </si>
+  <si>
+    <t>0.4404,0.1714,0.2539,0.3164</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1959,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2281,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,10 +2421,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2452,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2463,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2505,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2631,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2981,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3107,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3124,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3138,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3432,7 @@
         <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3600,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3712,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,10 +3793,10 @@
         <v>259</v>
       </c>
       <c r="C133" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3835,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3849,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3905,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4034,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4059,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,10 +4185,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4199,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4213,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4367,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,10 +4423,10 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4591,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4664,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4703,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4717,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4731,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4787,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4801,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4829,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,10 +5053,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5165,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>261</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,10 +5221,10 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5417,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5459,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
